--- a/03_Group_comparisons/HRvLR/c_data/07_module_preservation.xlsx
+++ b/03_Group_comparisons/HRvLR/c_data/07_module_preservation.xlsx
@@ -10,8 +10,8 @@
     <sheet name="read_me" sheetId="1" r:id="rId1"/>
     <sheet name="columns" sheetId="2" r:id="rId2"/>
     <sheet name="preservation" sheetId="3" r:id="rId3"/>
-    <sheet name="arm_networks" sheetId="4" r:id="rId4"/>
-    <sheet name="arm_membership" sheetId="5" r:id="rId5"/>
+    <sheet name="group_networks" sheetId="4" r:id="rId4"/>
+    <sheet name="group_membership" sheetId="5" r:id="rId5"/>
     <sheet name="input_manifest" sheetId="6" r:id="rId6"/>
     <sheet name="package_versions" sheetId="7" r:id="rId7"/>
   </sheets>
@@ -37,19 +37,19 @@
     <t>preservation</t>
   </si>
   <si>
-    <t>Zsummary and median rank of each arm's modules tested in the other arm.</t>
-  </si>
-  <si>
-    <t>arm_networks</t>
-  </si>
-  <si>
-    <t>Samples, soft power and module count of each arm's network.</t>
-  </si>
-  <si>
-    <t>arm_membership</t>
-  </si>
-  <si>
-    <t>Every protein's module in each arm's network.</t>
+    <t>Zsummary and median rank of each group's modules tested in the other group.</t>
+  </si>
+  <si>
+    <t>group_networks</t>
+  </si>
+  <si>
+    <t>Samples, soft power and module count of each group's network.</t>
+  </si>
+  <si>
+    <t>group_membership</t>
+  </si>
+  <si>
+    <t>Every protein's module in each group's network.</t>
   </si>
   <si>
     <t>input_manifest</t>
@@ -121,10 +121,10 @@
     <t>Zsummary band.</t>
   </si>
   <si>
-    <t>arm</t>
-  </si>
-  <si>
-    <t>Study group of the participant (HR or LR), or the cluster that replaces it in a cluster grouping.</t>
+    <t>group</t>
+  </si>
+  <si>
+    <t>Group the row belongs to: HR or LR, or C1 or C2 in a proteome grouping.</t>
   </si>
   <si>
     <t>n_samples</t>
@@ -5968,7 +5968,7 @@
     <t>01_Processing/03_Quantification/c_data/DAList_corrected.rds</t>
   </si>
   <si>
-    <t>4b7147a39661ba7f9ed17b81a9ef9a9b</t>
+    <t>44029c7b54c5cc454b37546acd46c065</t>
   </si>
   <si>
     <t>modules</t>
@@ -5977,7 +5977,7 @@
     <t>01_Processing/06_Module_Building/c_data/modules.rds</t>
   </si>
   <si>
-    <t>9062a97ff96fac52908895e0eeb7bf57</t>
+    <t>37335a295505b53dcf355baf87333202</t>
   </si>
   <si>
     <t>backports</t>
